--- a/data/1st Round/Corrected/CdS3_1_Results Table.xlsx
+++ b/data/1st Round/Corrected/CdS3_1_Results Table.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3804" yWindow="2340" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3312" yWindow="3312" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Corrected Results" sheetId="1" state="visible" r:id="rId1"/>
